--- a/10. Communicatie/sjabloon_links.xlsx
+++ b/10. Communicatie/sjabloon_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\JiveDocumentation\10. Communicatie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2D739A-B3EB-448F-B394-068951C7AE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514A90F6-A64F-4957-BDE6-51503AFBC58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{72F6FAE1-3AFF-42D1-9832-ACCCD42F5209}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72F6FAE1-3AFF-42D1-9832-ACCCD42F5209}"/>
   </bookViews>
   <sheets>
     <sheet name="verwijzen naar PinC" sheetId="4" r:id="rId1"/>
@@ -169,7 +169,7 @@
     <t>Eens we een URL hebben, voorzien we die van tracking codes, zodat we kunnen zien wat het effect is van communicatiecampagnes. Zie daarvoor het tweede tabblad!</t>
   </si>
   <si>
-    <t>https://provincies.incijfers.be/databank?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587</t>
+    <t>https://provincies.incijfers.be/viewer?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587</t>
   </si>
 </sst>
 </file>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -264,11 +264,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -611,127 +610,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
+      <c r="A2" s="10"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
+      <c r="A7" s="10"/>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
+      <c r="A12" s="10"/>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
+      <c r="A19" s="10"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
+      <c r="A26" s="10"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -751,10 +750,10 @@
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
+      <c r="A31" s="10"/>
     </row>
     <row r="32" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>32</v>
       </c>
     </row>
@@ -770,7 +769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A26CEBE2-0F8A-495C-89AB-A5AE077BA272}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.77734375" customWidth="1"/>
@@ -782,87 +781,68 @@
     <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="15" t="str">
+      <c r="B4" s="14" t="str">
         <f>CONCATENATE(CONCATENATE(IFERROR(MID(B1,1,FIND("#",B1)-1),B1),IFERROR(IF(FIND("?",IFERROR(MID(B1,1,FIND("#",B1)-1),B1))&gt;0,"&amp;","?"),"?"),"mtm_campaign=",B2,"&amp;mtm_kwd=",B3),IFERROR(MID(B1,FIND("#",B1),99),""))</f>
-        <v>https://provincies.incijfers.be/databank?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587&amp;mtm_campaign=pinc-nieuwsbrief-mei-2021&amp;mtm_kwd=afval-algemeen</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+        <v>https://provincies.incijfers.be/viewer?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587&amp;mtm_campaign=pinc-nieuwsbrief-mei-2021&amp;mtm_kwd=afval-algemeen</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" location="matomo-urls-opstellen" display="Klik voor meer details en voorbeelden" xr:uid="{7864DFD9-BBB1-4350-B370-478549C47A02}"/>
-    <hyperlink ref="B1" r:id="rId2" xr:uid="{1183021B-10FF-4AD0-BFBE-5F37ABE55BF6}"/>
+    <hyperlink ref="B1" r:id="rId2" display="https://provincies.incijfers.be/databank?jiveworkspace_guid=ff593898-a5fa-41de-bddc-ebf303c20587" xr:uid="{1183021B-10FF-4AD0-BFBE-5F37ABE55BF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -870,6 +850,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100936F8FED91617845B8AEE40909B55B39" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fdd048e5dac583385d85172ba3b74e7c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="50990e7d-986b-48ed-b7c7-e36476cb9bc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1746dd66c24095ee243b6b7578615d7" ns2:_="">
     <xsd:import namespace="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
@@ -1047,12 +1033,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1063,6 +1043,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD01876-4A38-4D89-AF61-D36C1FE0C3B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B20CB91D-FED1-447E-B613-85B1339A1856}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1080,22 +1076,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD01876-4A38-4D89-AF61-D36C1FE0C3B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="50990e7d-986b-48ed-b7c7-e36476cb9bc9"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FD8BEE-8873-449E-A338-98F2026C684D}">
   <ds:schemaRefs>
